--- a/TS3_note.xlsx
+++ b/TS3_note.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/TS3_note.xlsx
+++ b/TS3_note.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/TS3_note.xlsx
+++ b/TS3_note.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/TS3_note.xlsx
+++ b/TS3_note.xlsx
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/TS3_note.xlsx
+++ b/TS3_note.xlsx
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
